--- a/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:53</t>
+          <t>2026-08-26 16:01:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:54</t>
+          <t>2026-08-26 16:01:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:56</t>
+          <t>2026-08-26 16:01:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-26 15:54:57</t>
+          <t>2026-08-26 16:01:40</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.67%1,794,000</t>
+          <t>8.50%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.67%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.62%510,000</t>
+          <t>6.79%510,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>6.79%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.56%872,000</t>
+          <t>6.75%872,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.56%</t>
+          <t>6.75%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.96%3,850,000</t>
+          <t>6.04%3,850,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.35%186,000</t>
+          <t>5.30%186,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.67%4,809,000</t>
+          <t>3.82%4,809,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.63%322,000</t>
+          <t>3.72%322,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-10%5040</t>
+          <t>+0.76%1980</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5040</v>
+        <v>1980</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.46%307,000</t>
+          <t>3.30%849,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>307000</v>
+        <v>849000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.76%1980</t>
+          <t>+9.97%6290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+9.97%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1980</v>
+        <v>6290</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.36%849,000</t>
+          <t>3.18%258,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>849000</v>
+        <v>258000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.23%2055</t>
+          <t>-10%5040</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.23%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2055</v>
+        <v>5040</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.97%727,000</t>
+          <t>3.04%307,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>727000</v>
+        <v>307000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,25 +1114,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+9.97%6290</t>
+          <t>+4.57%916</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>+4.57%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6290</v>
+        <v>916</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.97%258,000</t>
+          <t>2.97%1,650,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>258000</v>
+        <v>1650000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.57%916</t>
+          <t>+1.23%2055</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.57%</t>
+          <t>+1.23%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>916</v>
+        <v>2055</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.91%1,650,000</t>
+          <t>2.93%727,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1650000</v>
+        <v>727000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.84%3,178,000</t>
+          <t>2.82%3,178,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.82%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.56%1,000,000</t>
+          <t>2.64%1,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:36</t>
+          <t>2026-08-26 17:23:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.26%381,000</t>
+          <t>2.36%381,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.22%1,123,000</t>
+          <t>2.09%1,123,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.97%3,302,000</t>
+          <t>1.99%3,302,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.62%1,158,000</t>
+          <t>1.68%1,158,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.2%123.5</t>
+          <t>+2.03%428</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>123.5</v>
+        <v>428</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.34%5,315,000</t>
+          <t>1.33%1,581,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>5315000</v>
+        <v>1581000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.03%428</t>
+          <t>+3.03%1530</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>428</v>
+        <v>1530</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.34%1,581,000</t>
+          <t>1.31%437,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1581000</v>
+        <v>437000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.64%180</t>
+          <t>-1.2%123.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>180</v>
+        <v>123.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.31%3,552,000</t>
+          <t>1.29%5,315,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3552000</v>
+        <v>5315000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.03%1530</t>
+          <t>+1.39%146</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1530</v>
+        <v>146</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.31%437,000</t>
+          <t>1.26%4,412,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>437000</v>
+        <v>4412000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.28%181</t>
+          <t>-1.64%180</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.29%3,524,000</t>
+          <t>1.25%3,552,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3524000</v>
+        <v>3552000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+1.39%146</t>
+          <t>-0.28%181</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.28%4,412,000</t>
+          <t>1.25%3,524,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>4412000</v>
+        <v>3524000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.27%1,811,000</t>
+          <t>1.25%1,811,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.24%3,453,000</t>
+          <t>1.23%3,453,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2428興勤</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1%252</t>
+          <t>+3.27%173.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>252</v>
+        <v>173.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.19%2,371,000</t>
+          <t>1.19%3,494,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2371000</v>
+        <v>3494000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>2428興勤</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.27%173.5</t>
+          <t>+1%252</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.27%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>173.5</v>
+        <v>252</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.18%3,494,000</t>
+          <t>1.17%2,371,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3494000</v>
+        <v>2371000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:38</t>
+          <t>2026-08-26 17:23:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.15%965,000</t>
+          <t>1.12%965,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.3%165.5</t>
+          <t>+6.54%570</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+6.54%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>165.5</v>
+        <v>570</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.14%3,416,000</t>
+          <t>1.12%1,000,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3416000</v>
+        <v>1000000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.88%15690</t>
+          <t>-0.3%165.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>15690</v>
+        <v>165.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.11%35,900</t>
+          <t>1.11%3,416,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>35900</v>
+        <v>3416000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2478大毅</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.24%122</t>
+          <t>+1.88%15690</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>122</v>
+        <v>15690</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.09%4,511,000</t>
+          <t>1.11%35,900</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>4511000</v>
+        <v>35900</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>2478大毅</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+6.54%570</t>
+          <t>+1.24%122</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+6.54%</t>
+          <t>+1.24%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>570</v>
+        <v>122</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.08%1,000,000</t>
+          <t>1.08%4,511,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1000000</v>
+        <v>4511000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.05%1,910,000</t>
+          <t>1.07%1,910,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.98%1,032,000</t>
+          <t>0.93%1,032,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.94%382,000</t>
+          <t>0.90%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+2.11%217.5</t>
+          <t>+1.74%262.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.11%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>217.5</v>
+        <v>262.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.88%2,042,000</t>
+          <t>0.83%1,607,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2042000</v>
+        <v>1607000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>5536聖暉*</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.74%262.5</t>
+          <t>+0.12%854</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>262.5</v>
+        <v>854</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.84%1,607,000</t>
+          <t>0.77%459,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1607000</v>
+        <v>459000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5536聖暉*</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.12%854</t>
+          <t>+9.79%2410</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+9.79%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>854</v>
+        <v>2410</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.79%459,000</t>
+          <t>0.44%93,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>459000</v>
+        <v>93000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+9.79%2410</t>
+          <t>+2.11%217.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+9.79%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2410</v>
+        <v>217.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.41%93,000</t>
+          <t>0.44%1,021,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>93000</v>
+        <v>1021000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+10%583</t>
+          <t>+9.9%96.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+9.9%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>583</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.34%322,000</t>
+          <t>0.43%2,249,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>322000</v>
+        <v>2249000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2476鉅祥</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.15%125.5</t>
+          <t>+10%583</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.15%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>125.5</v>
+        <v>583</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.32%1,311,000</t>
+          <t>0.37%322,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1311000</v>
+        <v>322000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>2476鉅祥</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.62%251.5</t>
+          <t>+4.15%125.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.62%</t>
+          <t>+4.15%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>251.5</v>
+        <v>125.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.31%612,000</t>
+          <t>0.32%1,311,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>612000</v>
+        <v>1311000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:39</t>
+          <t>2026-08-26 17:23:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.30%312,000</t>
+          <t>0.31%312,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.22%276.5</t>
+          <t>+1.62%251.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+1.62%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>276.5</v>
+        <v>251.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.30%549,000</t>
+          <t>0.30%612,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>549000</v>
+        <v>612000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,34 +3310,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8070長華*</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+4.06%51.3</t>
+          <t>+2.22%276.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+2.22%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>51.3</v>
+        <v>276.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.29%2,897,000</t>
+          <t>0.30%549,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2897000</v>
+        <v>549000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>8070長華*</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.64%62.8</t>
+          <t>+4.06%51.3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+4.06%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>62.8</v>
+        <v>51.3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.28%2,213,556</t>
+          <t>0.29%2,897,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2213556</v>
+        <v>2897000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+9.9%96.6</t>
+          <t>+0.64%62.8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>96.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.28%1,563,000</t>
+          <t>0.27%2,213,556</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1563000</v>
+        <v>2213556</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:40</t>
+          <t>2026-08-26 17:24:01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:57</t>
+          <t>2026-08-26 19:34:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:58</t>
+          <t>2026-08-26 19:34:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 17:23:59</t>
+          <t>2026-08-26 19:34:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-26 17:24:01</t>
+          <t>2026-08-26 19:34:11</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:07</t>
+          <t>2026-08-26 21:14:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:08</t>
+          <t>2026-08-26 21:14:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:09</t>
+          <t>2026-08-26 21:14:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-26 19:34:11</t>
+          <t>2026-08-26 21:14:59</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:55</t>
+          <t>2026-08-26 21:38:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:57</t>
+          <t>2026-08-26 21:38:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:58</t>
+          <t>2026-08-26 21:38:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-26 21:14:59</t>
+          <t>2026-08-26 21:38:19</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:15</t>
+          <t>2026-08-26 22:14:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:17</t>
+          <t>2026-08-26 22:14:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:18</t>
+          <t>2026-08-26 22:14:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-26 21:38:19</t>
+          <t>2026-08-26 22:14:06</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">

--- a/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-26_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:02</t>
+          <t>2026-08-26 22:19:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:03</t>
+          <t>2026-08-26 22:19:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:05</t>
+          <t>2026-08-26 22:19:19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-26 22:14:06</t>
+          <t>2026-08-26 22:19:21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
